--- a/ui-bulk-task-template.xlsx
+++ b/ui-bulk-task-template.xlsx
@@ -4419,7 +4419,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4458,6 +4458,11 @@
       <c r="L72" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/exam-day/page.tsx. Dark countdown chip in head, 4-card exam meta strip (cert/when/format/booking), blue gradient countdown card with days+hours+checklist progress, day-of checklist grouped by 4 categories (Identity/Tech/Environment/Policies) with check states, 5 PMI policies (numbered list), red watch-outs card, dark CTA banner linking to standby surface. Verified at /lms/pmp/exam-day.</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4482,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4486,7 +4491,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4516,6 +4521,11 @@
       <c r="L73" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/exam-day/active/page.tsx. Calm centered surface with LIVE/SOON pulsing status pill, big Join exam now green CTA (or yellow countdown numbers when soon), final reminders list (4 checks + 1 info), amber locked panel announcing that study tools are paused during the exam window, footer with support + outcome-recording links. Verified at /lms/pmp/exam-day/active.</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4545,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4544,7 +4554,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4574,6 +4584,11 @@
       <c r="L74" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/exam-result/record/page.tsx. Outcome picker tiles (Pass green / Fail red) with radio selection, 5-field form (date / score / booking ref / delivery method / notes), dashed upload zone for proof, sidebar showing What happens next per tier (Bronze repurchase, Silver 1x90d retake, Gold 2x180d + claim) + why-proof block + yellow one-time-entry warning. Verified at /lms/pmp/exam-result/record.</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4608,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4602,7 +4617,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4632,6 +4647,11 @@
       <c r="L75" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/certificate/page.tsx. Blue-themed certificate frame (double border + ornate corners + dashed PMI seal in centre + cursive signatures of Pierre Le Manh and Sunil Prashara) showing PMP certification number, score AT/AT/T, valid-through date. Sidebar: Download PDF + Share-on-LinkedIn + 4-icon share row, certificate details dl, three-link Whats next card (share / pathways / renewal). Verified at /lms/pmp/certificate.</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4671,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4660,7 +4680,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4690,6 +4710,11 @@
       <c r="L76" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/share/page.tsx. Three pre-built share cards (LinkedIn blue / X dark / WhatsApp green) with platform-accurate mockups: LinkedIn post with avatar+cert-attachment, X 280-char short, WhatsApp chat bubble in green theme. Edit + Post CTAs per card. Yellow referral payoff card with +Rs.600 bonus and copy-code button + cashback link. Dark Whats next footer. Verified at /lms/pmp/share.</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4734,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4718,7 +4743,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4748,6 +4773,11 @@
       <c r="L77" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/pathways/page.tsx. Six curated certifications (PgMP/PMI-ACP/PMI-RMP/PRINCE2 Practitioner/ITIL 4 DPI/Lean Six Sigma BB) in 3-col grid colour-keyed by track. Each card: difficulty pill (Advanced/Lateral/Specialise) + awarding body chip + Why-match green callout grounded in learner signals + colored CTA opening invensislearning.com. Top match highlighted on PgMP. Dark alumni-discount footer. Verified at /lms/pmp/pathways.</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4797,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4776,7 +4806,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4806,6 +4836,11 @@
       <c r="L78" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/renewal/page.tsx. Blue PDU progress hero (12/60) with cycle marker showing on-track vs behind, two category bars (Education 8/35 + Giving back 4/25), 4-entry PDU activity log auto-synced from PMI CCR, opportunity sidebar with 4 ways to earn (training/mentor/case study/webinars), dark What-happens-if-you-dont-renew footer linking to PMI CCR Handbook. Verified at /lms/pmp/renewal.</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4860,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4834,7 +4869,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4864,6 +4899,11 @@
       <c r="L79" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/exam-result/page.tsx. Empathetic Tough day. Heres the path forward header with Did not pass red pill, red-tinted score hero (54% with red marker at 60 pass mark + closest-cluster meta), tier card explaining tier-aware recovery, side-by-side path picker: Retake 180 days (green Recommended) + Money-back claim (amber Gate-honoured). Per-cluster weakness chart + Setback-not-verdict tone card. Verified at /lms/pmp/exam-result.</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4923,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4892,7 +4932,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4922,6 +4962,11 @@
       <c r="L80" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/retake/page.tsx. Window status hero (168 of 180 days left + voucher Re-issued pill), 3-cohort picker with capacity bars + recommended highlight, credit ledger card showing 4 included resources (training/Q-bank boost/extra mocks/coaching), 6-week suggested taper plan timeline, amber Not feeling the retake? banner offering claim alternative. Verified at /lms/pmp/retake.</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4986,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4950,7 +4995,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4980,6 +5025,11 @@
       <c r="L81" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/money-back/claim/page.tsx. Refund-amount green hero (Rs.23,000 = Rs.24,500 - Rs.1,500 cashback) with claim window meta, 6-item gate-honoured checklist mirror with snapshot-at-redemption columns (all OK in demo), 3 payout method radios, claim form with required proof upload, two required confirmation checkboxes, danger red Submit refund claim CTA (disabled until checkboxes ticked). How-claim-flows + Talk-to-coach sidebar. Verified at /lms/pmp/money-back/claim.</t>
         </is>
       </c>
     </row>
@@ -4999,7 +5049,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5008,7 +5058,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5038,6 +5088,11 @@
       <c r="L82" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/money-back/status/[claimId]/page.tsx. Dark refund hero (Rs.23,000 + claim meta + expected-by date), Currently-doing card spelling the active step, 4-step timeline with state-colored dots (done green / current blue pulsing / pending dashed / rejected red) and connecting line, dispute callout that only renders when rejected, audit receipt dl + What happens after refund sidebar. Verified at /lms/pmp/money-back/status/CLM-2026-7841.</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5112,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5066,7 +5121,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5096,6 +5151,11 @@
       <c r="L83" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/closed/page.tsx. Two terminal variants: PASSED — golden gradient hero with PMP-certified strong + trophy circle + Download/Share/Renewal CTAs; REFUNDED — dark hero with refund-amount card + re-enrol-at-alumni-rate. Both show 6-stat journey summary, 3-card pathways cross-sell (PgMP/PMI-ACP/LSSBB), green What-you-keep + grey Whats-archived split, warm Glad-you-came-through-with-us footer with alumni community CTA. Verified at /lms/pmp/closed.</t>
         </is>
       </c>
     </row>

--- a/ui-bulk-task-template.xlsx
+++ b/ui-bulk-task-template.xlsx
@@ -5175,7 +5175,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5214,6 +5214,11 @@
       <c r="L84" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/emails/page.tsx. Gallery of 8 static HTML email mockups (activation, welcome from Priya, receipt with GSTIN, voucher-issued with dashed code box, password reset, 3 nudge variants). Each in a real email frame. Categorised transactional/lifecycle/nudge. Verified at /emails.</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5238,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5242,7 +5247,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5272,6 +5277,11 @@
       <c r="L85" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/polish/page.tsx (instructor-modal section). Bio modal with avatar+rating row (4.9 stars, 1.2k reviews, 92% pass rate), 3-stat block, Certifications+Expertise+Recognition tag rows, 3 learner reviews, 3 upcoming sessions, fun-fact callout, Email + Book coaching CTAs. Triggered from any instructor name across Stage 5. Verified at /lms/pmp/polish.</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5301,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5300,7 +5310,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5330,6 +5340,11 @@
       <c r="L86" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Prototype shipped at /app/lms/[slug]/polish/page.tsx (celebration-banner section). Green-gradient banner with animated 10-dot burst, pulsing icon, 4-stat row, Redeem voucher primary + Open readiness ghost CTAs. Reduced-motion respected. Shown alongside the 2 other banner states. Verified at /lms/pmp/polish.</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5364,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5358,7 +5373,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5388,6 +5403,11 @@
       <c r="L87" t="inlineStr">
         <is>
           <t>Mayank</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>A11y + responsive pass documented at /A11Y.md. WCAG 2.2 AA: keyboard nav, focus return, screen-reader labels, semantic structure, 4.5:1 contrast, prefers-reduced-motion respected, breakpoints at 1100px tablet and 760px mobile (42 @media blocks across globals.css). Open issues noted (backend a11y deferred to T87-123).</t>
         </is>
       </c>
     </row>
